--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.82293572157293</v>
+        <v>9.396227054755601</v>
       </c>
       <c r="D2" t="n">
-        <v>57.58441959540279</v>
+        <v>9.357468184252953</v>
       </c>
       <c r="E2" t="n">
-        <v>18.38547611459479</v>
+        <v>2.987639868621654</v>
       </c>
       <c r="F2" t="n">
-        <v>19.93822724128557</v>
+        <v>3.239961926708905</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.91602444982769</v>
+        <v>7.136353973096999</v>
       </c>
       <c r="D3" t="n">
-        <v>45.74000565664021</v>
+        <v>7.432750919204035</v>
       </c>
       <c r="E3" t="n">
-        <v>18.38547611459479</v>
+        <v>2.987639868621654</v>
       </c>
       <c r="F3" t="n">
-        <v>19.93822724128557</v>
+        <v>3.239961926708905</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.16968029026386</v>
+        <v>7.340073047167878</v>
       </c>
       <c r="D4" t="n">
-        <v>11.70469991071963</v>
+        <v>1.902013735491939</v>
       </c>
       <c r="E4" t="n">
-        <v>18.38547611459479</v>
+        <v>2.987639868621654</v>
       </c>
       <c r="F4" t="n">
-        <v>19.93822724128557</v>
+        <v>3.239961926708905</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.18478771970077</v>
+        <v>2.305028004451374</v>
       </c>
       <c r="D5" t="n">
-        <v>12.97343718916513</v>
+        <v>2.108183543239334</v>
       </c>
       <c r="E5" t="n">
-        <v>18.38547611459479</v>
+        <v>2.987639868621654</v>
       </c>
       <c r="F5" t="n">
-        <v>19.93822724128557</v>
+        <v>3.239961926708905</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.45746534711329</v>
+        <v>1.86183811890591</v>
       </c>
       <c r="D6" t="n">
-        <v>10.48306202763975</v>
+        <v>1.70349757949146</v>
       </c>
       <c r="E6" t="n">
-        <v>18.38547611459479</v>
+        <v>2.987639868621654</v>
       </c>
       <c r="F6" t="n">
-        <v>19.93822724128557</v>
+        <v>3.239961926708905</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
